--- a/assets/js/ICMS ST - Mercadinho.xlsx
+++ b/assets/js/ICMS ST - Mercadinho.xlsx
@@ -2675,7 +2675,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela2" displayName="Tabela2" ref="D1:S1000" totalsRowShown="0" headerRowDxfId="62" dataDxfId="60" headerRowBorderDxfId="61" tableBorderDxfId="59" totalsRowBorderDxfId="58">
-  <autoFilter ref="D1:S1000" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Chave" dataDxfId="57"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="UF" dataDxfId="56"/>
@@ -2702,7 +2701,6 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela22" displayName="Tabela22" ref="D1:S1000" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41" totalsRowBorderDxfId="40">
-  <autoFilter ref="D1:S1000" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Chave" dataDxfId="39"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="UF" dataDxfId="38"/>
@@ -2729,7 +2727,6 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela224" displayName="Tabela224" ref="D1:S1000" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
-  <autoFilter ref="D1:S1000" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Chave" dataDxfId="21"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="UF" dataDxfId="20"/>
